--- a/crates/jxcel-export/tests/fixtures/nested.xlsx
+++ b/crates/jxcel-export/tests/fixtures/nested.xlsx
@@ -9,7 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="明細" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="合計セル">明細!$B$6</definedName>
+    <definedName name="グループ">明細!$A$3:$C$5</definedName>
+    <definedName name="別シート">Sheet9!$A$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'明細'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'明細'!$A$1:$D$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
